--- a/data/external/terminos/Lugares literarios.xlsx
+++ b/data/external/terminos/Lugares literarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dora\OneDrive\Desktop\Diccionarios literatura\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karen\Documents\HumanidadesDigitales_git\data\external\terminos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46792E58-5CB9-4244-9DDE-FEB9208A0B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C5B9CB-F908-458A-8679-8AF1ED157E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="215">
   <si>
     <t>Autor</t>
   </si>
@@ -610,6 +610,69 @@
   </si>
   <si>
     <t xml:space="preserve"> J.K. Rowling</t>
+  </si>
+  <si>
+    <t>Lugar_nombres</t>
+  </si>
+  <si>
+    <t>Callejón Diagon, Diagon Alley, Diagon</t>
+  </si>
+  <si>
+    <t>Bosque de los Cien Acres, Hundred Acre Wood</t>
+  </si>
+  <si>
+    <t>Estado Mundial</t>
+  </si>
+  <si>
+    <t>País de los juguetes, Juguetelandia</t>
+  </si>
+  <si>
+    <t>Casa de Jengibre y Golosinas, Casa de Jengibre</t>
+  </si>
+  <si>
+    <t>Hogwarts</t>
+  </si>
+  <si>
+    <t>El País de Nunca Jamás, Neverland</t>
+  </si>
+  <si>
+    <t>Ribera del río, River Bank</t>
+  </si>
+  <si>
+    <t>País de las maravillas, Wonderland</t>
+  </si>
+  <si>
+    <t>La Comarca, Comarca</t>
+  </si>
+  <si>
+    <t>Prados y Cabaña de los Alpes, Casa del Abuelo, Cabaña de Heidi</t>
+  </si>
+  <si>
+    <t>La Casa de la Encarnación, Casa de Ejercicios Espirituales de la Encarnación</t>
+  </si>
+  <si>
+    <t>Ciudad Fantasía, Fantastica, La torre de Marfil</t>
+  </si>
+  <si>
+    <t>San Francisco Post-apocalíptico,  San Francisco postapocalíptico</t>
+  </si>
+  <si>
+    <t>Fábrica de Willy Wonka, Fábrica de chocolate</t>
+  </si>
+  <si>
+    <t>Mundodisco, Discworld</t>
+  </si>
+  <si>
+    <t>Valle Mumin, Moomin Valley</t>
+  </si>
+  <si>
+    <t>Terramar, Earthsea</t>
+  </si>
+  <si>
+    <t>Invierno Gethen, Gethen</t>
+  </si>
+  <si>
+    <t>Condado de Yoknapatawpha, Yoknapatawpha</t>
   </si>
 </sst>
 </file>
@@ -937,16 +1000,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,8 +1022,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>193</v>
       </c>
@@ -973,8 +1039,11 @@
       <c r="D2" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>148</v>
       </c>
@@ -987,8 +1056,11 @@
       <c r="D3" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>52</v>
       </c>
@@ -1001,8 +1073,11 @@
       <c r="D4" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1015,8 +1090,11 @@
       <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>156</v>
       </c>
@@ -1029,8 +1107,11 @@
       <c r="D6" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>112</v>
       </c>
@@ -1043,8 +1124,11 @@
       <c r="D7" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>116</v>
       </c>
@@ -1057,8 +1141,11 @@
       <c r="D8" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
@@ -1071,8 +1158,11 @@
       <c r="D9" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>45</v>
       </c>
@@ -1085,8 +1175,11 @@
       <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
@@ -1099,8 +1192,11 @@
       <c r="D11" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
@@ -1113,8 +1209,11 @@
       <c r="D12" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
@@ -1127,8 +1226,11 @@
       <c r="D13" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>72</v>
       </c>
@@ -1141,8 +1243,11 @@
       <c r="D14" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>72</v>
       </c>
@@ -1155,8 +1260,11 @@
       <c r="D15" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>170</v>
       </c>
@@ -1169,8 +1277,11 @@
       <c r="D16" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1183,8 +1294,11 @@
       <c r="D17" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>138</v>
       </c>
@@ -1197,8 +1311,11 @@
       <c r="D18" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>136</v>
       </c>
@@ -1211,8 +1328,11 @@
       <c r="D19" s="1" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1225,8 +1345,11 @@
       <c r="D20" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1239,8 +1362,11 @@
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -1253,8 +1379,11 @@
       <c r="D22" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1267,8 +1396,11 @@
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>174</v>
       </c>
@@ -1281,8 +1413,11 @@
       <c r="D24" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>104</v>
       </c>
@@ -1295,8 +1430,11 @@
       <c r="D25" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
@@ -1309,8 +1447,11 @@
       <c r="D26" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>92</v>
       </c>
@@ -1323,8 +1464,11 @@
       <c r="D27" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>164</v>
       </c>
@@ -1337,8 +1481,11 @@
       <c r="D28" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>160</v>
       </c>
@@ -1351,8 +1498,11 @@
       <c r="D29" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>120</v>
       </c>
@@ -1365,8 +1515,11 @@
       <c r="D30" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>120</v>
       </c>
@@ -1379,8 +1532,11 @@
       <c r="D31" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>120</v>
       </c>
@@ -1393,8 +1549,11 @@
       <c r="D32" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>186</v>
       </c>
@@ -1407,8 +1566,11 @@
       <c r="D33" s="1" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>30</v>
       </c>
@@ -1421,8 +1583,11 @@
       <c r="D34" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>60</v>
       </c>
@@ -1435,8 +1600,11 @@
       <c r="D35" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>64</v>
       </c>
@@ -1449,8 +1617,11 @@
       <c r="D36" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>178</v>
       </c>
@@ -1463,8 +1634,11 @@
       <c r="D37" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>144</v>
       </c>
@@ -1477,8 +1651,11 @@
       <c r="D38" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>26</v>
       </c>
@@ -1491,8 +1668,11 @@
       <c r="D39" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>84</v>
       </c>
@@ -1505,8 +1685,11 @@
       <c r="D40" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>124</v>
       </c>
@@ -1519,8 +1702,11 @@
       <c r="D41" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>68</v>
       </c>
@@ -1533,8 +1719,11 @@
       <c r="D42" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>34</v>
       </c>
@@ -1547,8 +1736,11 @@
       <c r="D43" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>128</v>
       </c>
@@ -1561,8 +1753,11 @@
       <c r="D44" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>132</v>
       </c>
@@ -1575,8 +1770,11 @@
       <c r="D45" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>182</v>
       </c>
@@ -1589,8 +1787,11 @@
       <c r="D46" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>14</v>
       </c>
@@ -1603,8 +1804,11 @@
       <c r="D47" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -1617,8 +1821,11 @@
       <c r="D48" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>14</v>
       </c>
@@ -1631,8 +1838,11 @@
       <c r="D49" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,8 +1855,11 @@
       <c r="D50" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>14</v>
       </c>
@@ -1659,8 +1872,11 @@
       <c r="D51" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>14</v>
       </c>
@@ -1673,8 +1889,11 @@
       <c r="D52" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>100</v>
       </c>
@@ -1687,8 +1906,11 @@
       <c r="D53" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>108</v>
       </c>
@@ -1700,6 +1922,9 @@
       </c>
       <c r="D54" s="1" t="s">
         <v>111</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
